--- a/fhir/finnish-smart/StructureDefinition-fi-smart-medication-request.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-medication-request.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-medication-request.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-medication-request.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -724,7 +724,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-medication|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-patient-medication)
+    <t xml:space="preserve">Reference(Substance|https://hl7.fi/fhir/finnish-base-profiles/StructureDefinition/fi-base-medication)
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="148.640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.80078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
